--- a/datos_afiliados.xlsx
+++ b/datos_afiliados.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B13"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -412,7 +412,7 @@
         <v>RC</v>
       </c>
       <c r="B2" t="str">
-        <v>1055274915</v>
+        <v>1055274915_x000d_</v>
       </c>
     </row>
     <row r="3">
@@ -420,7 +420,7 @@
         <v>TI</v>
       </c>
       <c r="B3" t="str">
-        <v>1011210568</v>
+        <v>1011210568_x000d_</v>
       </c>
     </row>
     <row r="4">
@@ -428,7 +428,7 @@
         <v>CC</v>
       </c>
       <c r="B4" t="str">
-        <v>12658</v>
+        <v>12658_x000d_</v>
       </c>
     </row>
     <row r="5">
@@ -436,7 +436,7 @@
         <v>CC</v>
       </c>
       <c r="B5" t="str">
-        <v>9513594</v>
+        <v>9513594_x000d_</v>
       </c>
     </row>
     <row r="6">
@@ -444,12 +444,68 @@
         <v>CC</v>
       </c>
       <c r="B6" t="str">
-        <v>23556241</v>
+        <v>23556241_x000d_</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>CC_x000d_</v>
+      </c>
+      <c r="B7" t="str">
+        <v>19082926_x000d_</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>CC_x000d_</v>
+      </c>
+      <c r="B8" t="str">
+        <v>9511215_x000d_</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>CC_x000d_</v>
+      </c>
+      <c r="B9" t="str">
+        <v>1053348031_x000d_</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>CC_x000d_</v>
+      </c>
+      <c r="B10" t="str">
+        <v>4264656_x000d_</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>CC_x000d_</v>
+      </c>
+      <c r="B11" t="str">
+        <v>20161653_x000d_</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>CC_x000d_</v>
+      </c>
+      <c r="B12" t="str">
+        <v>23485006_x000d_</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>CC</v>
+      </c>
+      <c r="B13" t="str">
+        <v>74130336</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B13"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/datos_afiliados.xlsx
+++ b/datos_afiliados.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B1"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -407,105 +407,9 @@
         <v>Documento_x000d_</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>RC</v>
-      </c>
-      <c r="B2" t="str">
-        <v>1055274915_x000d_</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>TI</v>
-      </c>
-      <c r="B3" t="str">
-        <v>1011210568_x000d_</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>CC</v>
-      </c>
-      <c r="B4" t="str">
-        <v>12658_x000d_</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>CC</v>
-      </c>
-      <c r="B5" t="str">
-        <v>9513594_x000d_</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>CC</v>
-      </c>
-      <c r="B6" t="str">
-        <v>23556241_x000d_</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>CC_x000d_</v>
-      </c>
-      <c r="B7" t="str">
-        <v>19082926_x000d_</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>CC_x000d_</v>
-      </c>
-      <c r="B8" t="str">
-        <v>9511215_x000d_</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>CC_x000d_</v>
-      </c>
-      <c r="B9" t="str">
-        <v>1053348031_x000d_</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>CC_x000d_</v>
-      </c>
-      <c r="B10" t="str">
-        <v>4264656_x000d_</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>CC_x000d_</v>
-      </c>
-      <c r="B11" t="str">
-        <v>20161653_x000d_</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>CC_x000d_</v>
-      </c>
-      <c r="B12" t="str">
-        <v>23485006_x000d_</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>CC</v>
-      </c>
-      <c r="B13" t="str">
-        <v>74130336</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/datos_afiliados.xlsx
+++ b/datos_afiliados.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -407,9 +407,25 @@
         <v>Documento_x000d_</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>CC_x000d_</v>
+      </c>
+      <c r="B2" t="str">
+        <v>28553526_x000d_</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>CC_x000d_</v>
+      </c>
+      <c r="B3" t="str">
+        <v>21210593</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B3"/>
   </ignoredErrors>
 </worksheet>
 </file>